--- a/data/trans_dic/P1802_2016_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1802_2016_2023-Clase-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,49; 20,25</t>
+          <t>12,37; 20,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,49; 21,44</t>
+          <t>13,47; 19,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,66; 19,89</t>
+          <t>11,65; 19,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,3; 25,85</t>
+          <t>19,42; 25,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,08; 18,4</t>
+          <t>13,34; 18,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,46; 22,25</t>
+          <t>16,96; 21,66</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,6%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,16; 16,04</t>
+          <t>9,48; 16,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,78; 20,67</t>
+          <t>12,04; 18,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,38; 21,56</t>
+          <t>13,74; 21,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,32; 24,21</t>
+          <t>17,07; 23,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,4; 17,8</t>
+          <t>12,21; 17,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,92; 21,04</t>
+          <t>15,35; 19,93</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,34; 18,81</t>
+          <t>12,45; 18,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,79; 78,78</t>
+          <t>12,3; 18,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,0; 31,88</t>
+          <t>18,17; 32,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,97; 27,33</t>
+          <t>16,8; 27,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,75; 20,55</t>
+          <t>14,92; 20,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,59; 72,92</t>
+          <t>14,69; 20,12</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>19,0%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,28; 17,61</t>
+          <t>13,32; 17,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,39; 20,22</t>
+          <t>14,9; 19,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,55; 22,15</t>
+          <t>16,77; 22,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,2; 21,75</t>
+          <t>19,26; 23,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,39; 18,69</t>
+          <t>15,22; 18,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,94; 19,78</t>
+          <t>17,35; 20,79</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -952,39 +952,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,64; 16,83</t>
+          <t>11,11; 16,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,54; 19,51</t>
+          <t>11,25; 17,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,32; 21,88</t>
+          <t>16,1; 22,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,71; 19,38</t>
+          <t>16,18; 20,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,61; 18,69</t>
+          <t>14,48; 18,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,21; 18,14</t>
+          <t>14,91; 18,48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,63; 13,83</t>
+          <t>6,7; 14,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,95; 9,71</t>
+          <t>1,91; 8,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,23; 22,03</t>
+          <t>17,42; 22,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,8; 16,3</t>
+          <t>11,65; 16,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,57; 19,83</t>
+          <t>15,66; 20,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,85; 13,63</t>
+          <t>9,99; 13,81</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,28; 15,71</t>
+          <t>13,21; 15,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,47; 36,66</t>
+          <t>13,86; 16,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,67; 20,51</t>
+          <t>17,68; 20,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,27; 19,01</t>
+          <t>17,83; 20,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,76; 17,64</t>
+          <t>15,8; 17,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,22; 29,15</t>
+          <t>16,22; 17,96</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>88948</t>
+          <t>90010</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99680</t>
+          <t>108995</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>188628</t>
+          <t>199005</t>
         </is>
       </c>
     </row>
@@ -1344,32 +1344,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>53581; 86888</t>
+          <t>53095; 86317</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>73104; 108140</t>
+          <t>74077; 109340</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40474; 69027</t>
+          <t>40433; 68951</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>86260; 115528</t>
+          <t>94725; 125191</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>101527; 142794</t>
+          <t>103571; 143689</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>166138; 211725</t>
+          <t>175981; 224729</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>74290</t>
+          <t>73929</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78286</t>
+          <t>85439</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>152576</t>
+          <t>159368</t>
         </is>
       </c>
     </row>
@@ -1462,32 +1462,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34571; 60491</t>
+          <t>35751; 62630</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57773; 93481</t>
+          <t>58166; 91061</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49805; 80268</t>
+          <t>51164; 80662</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66145; 92447</t>
+          <t>72112; 100309</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>92952; 133431</t>
+          <t>91486; 133242</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>132753; 175494</t>
+          <t>139034; 180474</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>311858</t>
+          <t>71777</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35873</t>
+          <t>40291</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>347731</t>
+          <t>112068</t>
         </is>
       </c>
     </row>
@@ -1580,32 +1580,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>64422; 98180</t>
+          <t>64985; 98219</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>98857; 526426</t>
+          <t>57986; 89034</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29895; 52966</t>
+          <t>30179; 53625</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28322; 45609</t>
+          <t>31504; 52023</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>101467; 141420</t>
+          <t>102689; 144140</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>138584; 609025</t>
+          <t>96854; 132591</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>182962</t>
+          <t>194596</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>162739</t>
+          <t>183675</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>345702</t>
+          <t>378271</t>
         </is>
       </c>
     </row>
@@ -1698,32 +1698,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>152697; 202458</t>
+          <t>153080; 201431</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>159164; 209090</t>
+          <t>168569; 221209</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>136710; 182947</t>
+          <t>138535; 182863</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>80067; 212467</t>
+          <t>165644; 206061</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>303990; 369177</t>
+          <t>300629; 369346</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>240040; 397671</t>
+          <t>345483; 413841</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>74983</t>
+          <t>81107</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>137320</t>
+          <t>151956</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>212304</t>
+          <t>233063</t>
         </is>
       </c>
     </row>
@@ -1816,39 +1816,39 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>72274; 104472</t>
+          <t>68973; 104523</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>59570; 92659</t>
+          <t>63873; 99748</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>120518; 161555</t>
+          <t>118841; 162836</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>106957; 163025</t>
+          <t>134404; 169273</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>198565; 253928</t>
+          <t>196746; 252489</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>173888; 238850</t>
+          <t>208602; 258538</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>105303</t>
+          <t>115432</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>116216</t>
+          <t>125549</t>
         </is>
       </c>
     </row>
@@ -1934,32 +1934,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19042; 39714</t>
+          <t>19251; 40358</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4683; 23348</t>
+          <t>4521; 20201</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>186401; 238388</t>
+          <t>188474; 240809</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>89735; 123979</t>
+          <t>98281; 136557</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>213203; 271446</t>
+          <t>214440; 274891</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>98650; 136489</t>
+          <t>107925; 149304</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>743956</t>
+          <t>521537</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>619202</t>
+          <t>685787</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1363157</t>
+          <t>1207324</t>
         </is>
       </c>
     </row>
@@ -2052,32 +2052,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>449743; 531761</t>
+          <t>447292; 532357</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>522012; 1237063</t>
+          <t>476731; 563912</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>623933; 724227</t>
+          <t>624558; 723218</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>509976; 679388</t>
+          <t>647537; 727178</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1090399; 1220046</t>
+          <t>1092846; 1220016</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1126807; 2025922</t>
+          <t>1146992; 1270614</t>
         </is>
       </c>
     </row>
